--- a/outputs/Smooth/Smooth - Low N_d_report.xlsx
+++ b/outputs/Smooth/Smooth - Low N_d_report.xlsx
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>4.172994421176378</v>
+        <v>4.145551468288782</v>
       </c>
       <c r="E4" t="n">
-        <v>4.17566789921879</v>
+        <v>4.092831296082062</v>
       </c>
       <c r="F4" t="n">
-        <v>37.59999999999997</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48.81621951594637</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>4.304092751121213</v>
+        <v>4.227340440014463</v>
       </c>
       <c r="E5" t="n">
-        <v>4.167789507703533</v>
+        <v>4.154554186886992</v>
       </c>
       <c r="F5" t="n">
-        <v>255.9263815791546</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>62.05452895985925</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>4.463346207343398</v>
+        <v>4.513812631424143</v>
       </c>
       <c r="E6" t="n">
-        <v>4.281589891527614</v>
+        <v>4.380907352679139</v>
       </c>
       <c r="F6" t="n">
-        <v>-147.0623010144284</v>
+        <v>-145</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.98895873660244</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>4.138416035283892</v>
+        <v>3.972050458266767</v>
       </c>
       <c r="E7" t="n">
-        <v>4.496754589911183</v>
+        <v>4.3294645468323</v>
       </c>
       <c r="F7" t="n">
-        <v>438.0653966728117</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44.9900628629422</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>4.127896904402459</v>
+        <v>3.954583281811226</v>
       </c>
       <c r="E8" t="n">
-        <v>4.508848721400578</v>
+        <v>4.331949174496654</v>
       </c>
       <c r="F8" t="n">
-        <v>527.7588570055306</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52.74851286753498</v>
+        <v>53</v>
       </c>
       <c r="D9" t="n">
-        <v>3.715513942673389</v>
+        <v>3.714699413119244</v>
       </c>
       <c r="E9" t="n">
-        <v>4.05763855661721</v>
+        <v>4.056518383942032</v>
       </c>
       <c r="F9" t="n">
-        <v>268.0075057623437</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>220.2</v>
+        <v>220</v>
       </c>
       <c r="D12" t="n">
-        <v>4.824605562067939</v>
+        <v>4.852886973687657</v>
       </c>
       <c r="E12" t="n">
-        <v>5.78262578661549</v>
+        <v>5.828483723674654</v>
       </c>
       <c r="F12" t="n">
-        <v>178.3</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>176.4828773324292</v>
+        <v>176</v>
       </c>
       <c r="D13" t="n">
-        <v>4.979785459207988</v>
+        <v>4.977946836303451</v>
       </c>
       <c r="E13" t="n">
-        <v>5.96205459351767</v>
+        <v>5.961760775558902</v>
       </c>
       <c r="F13" t="n">
-        <v>164.503182125261</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>199.900011744589</v>
+        <v>200</v>
       </c>
       <c r="D14" t="n">
-        <v>4.45365291972522</v>
+        <v>4.45364514835497</v>
       </c>
       <c r="E14" t="n">
-        <v>5.555955775915553</v>
+        <v>5.555617489155932</v>
       </c>
       <c r="F14" t="n">
-        <v>-104.3288164300387</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>115.7776331355991</v>
+        <v>116</v>
       </c>
       <c r="D15" t="n">
-        <v>4.963021418254815</v>
+        <v>4.963962763723101</v>
       </c>
       <c r="E15" t="n">
-        <v>6.05573386984006</v>
+        <v>6.05521243363794</v>
       </c>
       <c r="F15" t="n">
-        <v>820.1952828115465</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>104.1998698220392</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>5.010493346043185</v>
+        <v>5.00809880086083</v>
       </c>
       <c r="E16" t="n">
-        <v>6.078736467075245</v>
+        <v>6.068001467913191</v>
       </c>
       <c r="F16" t="n">
-        <v>871.6757545303918</v>
+        <v>873</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>139.646168236032</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
-        <v>4.504737842847931</v>
+        <v>4.500586489828124</v>
       </c>
       <c r="E17" t="n">
-        <v>5.627153122864397</v>
+        <v>5.625624459278212</v>
       </c>
       <c r="F17" t="n">
-        <v>565.5846729441279</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>418.0000002682208</v>
+        <v>418</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9514411166035551</v>
+        <v>0.9514410492807236</v>
       </c>
       <c r="E21" t="n">
-        <v>1.240033918506966</v>
+        <v>1.240033797457528</v>
       </c>
       <c r="F21" t="n">
-        <v>226.0000408197926</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>636.0000447799264</v>
+        <v>636</v>
       </c>
       <c r="D22" t="n">
-        <v>1.24048587045643</v>
+        <v>1.24048576226352</v>
       </c>
       <c r="E22" t="n">
-        <v>1.219237321728134</v>
+        <v>1.219237196611763</v>
       </c>
       <c r="F22" t="n">
-        <v>-449.0000445421914</v>
+        <v>-449</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>159.8536585365854</v>
+        <v>160</v>
       </c>
       <c r="D23" t="n">
-        <v>1.470698035489191</v>
+        <v>1.470375697464048</v>
       </c>
       <c r="E23" t="n">
-        <v>1.492558351720404</v>
+        <v>1.492410191422523</v>
       </c>
       <c r="F23" t="n">
-        <v>966.1463414634146</v>
+        <v>966</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>143.8682926829268</v>
+        <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>1.54153500375056</v>
+        <v>1.539652886575962</v>
       </c>
       <c r="E24" t="n">
-        <v>1.548573465471941</v>
+        <v>1.546563064216945</v>
       </c>
       <c r="F24" t="n">
-        <v>1003.031707317073</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>262.16</v>
+        <v>262</v>
       </c>
       <c r="D25" t="n">
-        <v>0.927005047179119</v>
+        <v>0.9276632804841615</v>
       </c>
       <c r="E25" t="n">
-        <v>1.045855271944391</v>
+        <v>1.046179407442378</v>
       </c>
       <c r="F25" t="n">
-        <v>679.6399999999999</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>
